--- a/data/reports/2024-05-20/2024-05-20_duplicates.xlsx
+++ b/data/reports/2024-05-20/2024-05-20_duplicates.xlsx
@@ -145,7 +145,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004723</t>
+    <t>RMD0005813</t>
   </si>
   <si>
     <t>CoreTel Communications, Inc.</t>
@@ -161,28 +161,28 @@
     <t>Core Communications, Inc., Ton80 Communications, LLC, CoreTel Alabama, Inc., CoreTel Delaware, Inc., CoreTel Florida, Inc., CoreTel Georgia, Inc., CoreTel Kansas, Inc., CoreTel Kentucky, Inc., CoreTel Massachusetts, Inc., CoreTel New Jersey, Inc., CoreTel Virginia, Inc., CoreTel West Virginia, Inc., CoreTel Washington, Inc.,</t>
   </si>
   <si>
+    <t>Glenn Dalgliesh</t>
+  </si>
+  <si>
+    <t>VP of Operations</t>
+  </si>
+  <si>
+    <t>NOC</t>
+  </si>
+  <si>
+    <t>'+14439121000</t>
+  </si>
+  <si>
+    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004723</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005813</t>
-  </si>
-  <si>
-    <t>Glenn Dalgliesh</t>
-  </si>
-  <si>
-    <t>VP of Operations</t>
-  </si>
-  <si>
-    <t>NOC</t>
-  </si>
-  <si>
-    <t>'+14439121000</t>
-  </si>
-  <si>
-    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004139</t>
@@ -225,10 +225,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008972</t>
+  </si>
+  <si>
+    <t>Media Flint, Inc.</t>
+  </si>
+  <si>
+    <t>15260 Ventura Boulevard
+Suite 1200 PMB 492
+Sherman Oaks California 91403</t>
+  </si>
+  <si>
+    <t>U.S. Virgin Islands</t>
+  </si>
+  <si>
+    <t>AvidTrak</t>
+  </si>
+  <si>
+    <t>null
+null CA
+California</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008973</t>
-  </si>
-  <si>
-    <t>Media Flint, Inc.</t>
   </si>
   <si>
     <t>15260 Ventura Boulevard
@@ -236,32 +258,10 @@
 Sherman Oaks CA 91403</t>
   </si>
   <si>
-    <t>U.S. Virgin Islands</t>
-  </si>
-  <si>
-    <t>AvidTrak</t>
-  </si>
-  <si>
-    <t>null
-null CA
-California</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008972</t>
-  </si>
-  <si>
-    <t>15260 Ventura Boulevard
-Suite 1200 PMB 492
-Sherman Oaks California 91403</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009020</t>
+    <t>RMD0009019</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -277,6 +277,24 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>208-947-3900</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009020</t>
+  </si>
+  <si>
     <t>IT Department</t>
   </si>
   <si>
@@ -286,25 +304,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009019</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>208-947-3900</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009205</t>
+    <t>RMD0009084</t>
   </si>
   <si>
     <t>ADCOM Technologies, LLC</t>
@@ -318,6 +318,12 @@
     <t>ON DEMAND Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009205</t>
+  </si>
+  <si>
     <t>Dean Franks</t>
   </si>
   <si>
@@ -340,13 +346,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=53ad1e731b53b0109294113d9c4bcb6a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009084</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008869</t>
+    <t>RMD0006774</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -356,9 +356,18 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>NONE</t>
+  </si>
+  <si>
     <t>Sage Network &amp; Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008869</t>
+  </si>
+  <si>
     <t>Rick Minyard</t>
   </si>
   <si>
@@ -378,15 +387,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006774</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004389</t>
@@ -469,10 +469,20 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1f0635261b85f81002beea82f54bcbec&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0005785</t>
+  </si>
+  <si>
+    <t>Edge Fibernet</t>
+  </si>
+  <si>
+    <t>5004 4th Avenue
+Brooklyn New York 11220</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0005786</t>
-  </si>
-  <si>
-    <t>Edge Fibernet</t>
   </si>
   <si>
     <t>254 36th Street
@@ -483,16 +493,6 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005785</t>
-  </si>
-  <si>
-    <t>5004 4th Avenue
-Brooklyn New York 11220</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0007488</t>
   </si>
   <si>
@@ -596,7 +596,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=89cc84f51b4af01068d1a82eac4bcb3e&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004701</t>
+    <t>RMD0003052</t>
   </si>
   <si>
     <t>Jaintel LLC</t>
@@ -606,15 +606,33 @@
 DE 19806-3334 Wilmington, United States</t>
   </si>
   <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>Elayaraja Jinadoss</t>
   </si>
   <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>'+447341664829</t>
+  </si>
+  <si>
+    <t>2024-05-01</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004701</t>
+  </si>
+  <si>
     <t>Operations Director</t>
   </si>
   <si>
-    <t>Management</t>
-  </si>
-  <si>
     <t>'+1 737 237 0913</t>
   </si>
   <si>
@@ -622,24 +640,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b1f3904a1b4138107ccf20ecac4bcbbf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003052</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>'+447341664829</t>
-  </si>
-  <si>
-    <t>2024-05-01</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0003053</t>
@@ -670,7 +670,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003444</t>
+    <t>RMD0003442</t>
   </si>
   <si>
     <t>Shaw Telecom GP</t>
@@ -681,32 +681,6 @@
   </si>
   <si>
     <t>Canada</t>
-  </si>
-  <si>
-    <t>0031064868; 0031064884; 0031064900</t>
-  </si>
-  <si>
-    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
-  </si>
-  <si>
-    <t>Network Operations</t>
-  </si>
-  <si>
-    <t>TOPS-NR&amp;A</t>
-  </si>
-  <si>
-    <t>2728 Hopewell Place N.E.
-Calgary AE 17724
-Alberta</t>
-  </si>
-  <si>
-    <t>'+1-866-244-7475</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003442</t>
   </si>
   <si>
     <t>0031064868;
@@ -726,6 +700,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=322c4e941b8df0509294113d9c4bcb51&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0003444</t>
+  </si>
+  <si>
+    <t>0031064868; 0031064884; 0031064900</t>
+  </si>
+  <si>
+    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
+  </si>
+  <si>
+    <t>Network Operations</t>
+  </si>
+  <si>
+    <t>TOPS-NR&amp;A</t>
+  </si>
+  <si>
+    <t>2728 Hopewell Place N.E.
+Calgary AE 17724
+Alberta</t>
+  </si>
+  <si>
+    <t>'+1-866-244-7475</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007384</t>
   </si>
   <si>
@@ -754,7 +754,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008577</t>
+    <t>RMD0005040</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -764,6 +764,12 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008577</t>
+  </si>
+  <si>
     <t>BatchDialer</t>
   </si>
   <si>
@@ -780,12 +786,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005040</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005569</t>
@@ -836,7 +836,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612913461bd6f010ca5aec21f54bcbac&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
+    <t>RMD0005297</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -849,6 +849,12 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007936</t>
+  </si>
+  <si>
     <t>Syed Omar Farooq Shah</t>
   </si>
   <si>
@@ -858,13 +864,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005585</t>
+    <t>RMD0005574</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -878,6 +878,22 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
+  </si>
+  <si>
+    <t>187 Plymouth Ave
+Fall River MA 02721</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005585</t>
+  </si>
+  <si>
     <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
   </si>
   <si>
@@ -891,23 +907,7 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005574</t>
-  </si>
-  <si>
-    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
-  </si>
-  <si>
-    <t>187 Plymouth Ave
-Fall River MA 02721</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007962</t>
@@ -993,7 +993,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007696</t>
+    <t>RMD0007716</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -1003,16 +1003,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007696</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007716</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -1022,6 +1022,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -1035,12 +1041,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008423</t>
@@ -1074,7 +1074,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008451</t>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1084,12 +1084,6 @@
 Greensboro NC 27401</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
     <t>null
 null NC</t>
   </si>
@@ -1097,6 +1091,12 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008451</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008611</t>
   </si>
   <si>
@@ -1116,25 +1116,25 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008612</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008610</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008759</t>
@@ -6083,16 +6083,28 @@
         <v>46</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="M5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R5" s="1" t="s">
         <v>26</v>
       </c>
@@ -6100,16 +6112,16 @@
         <v>26</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1">
         <v>17118795</v>
@@ -6133,28 +6145,16 @@
         <v>46</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
         <v>26</v>
       </c>
@@ -6162,7 +6162,7 @@
         <v>26</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1" t="s">
@@ -6431,9 +6431,11 @@
       <c r="O11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="Q11" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>30</v>
@@ -6444,14 +6446,16 @@
       <c r="T11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="V11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6478,7 +6482,7 @@
         <v>82</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>80</v>
@@ -6487,13 +6491,11 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>30</v>
@@ -6504,9 +6506,7 @@
       <c r="T12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>91</v>
       </c>
@@ -6525,55 +6525,41 @@
         <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q13" s="1"/>
       <c r="R13" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B14" s="1">
         <v>23003460</v>
@@ -6585,32 +6571,46 @@
         <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
+      <c r="Q14" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R14" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
@@ -6636,54 +6636,40 @@
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1">
         <v>23250467</v>
@@ -6700,33 +6686,47 @@
       <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U16" s="1"/>
       <c r="V16" s="1" t="s">
         <v>118</v>
       </c>
@@ -6892,13 +6892,13 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>127</v>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>26</v>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>26</v>
@@ -7377,55 +7377,61 @@
         <v>184</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+        <v>185</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="J29" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
         <v>39</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B30" s="1">
         <v>30758643</v>
@@ -7437,34 +7443,28 @@
         <v>184</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>193</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>192</v>
+        <v>27</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>194</v>
@@ -7474,10 +7474,10 @@
         <v>39</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>26</v>
@@ -7506,7 +7506,7 @@
         <v>30</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -7552,7 +7552,7 @@
         <v>30</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -7570,14 +7570,14 @@
         <v>199</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>204</v>
       </c>
       <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>30</v>
@@ -7619,45 +7619,33 @@
       <c r="I33" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>213</v>
-      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>215</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1">
         <v>31064850</v>
@@ -7675,30 +7663,42 @@
         <v>209</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="Q34" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R34" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U34" s="1"/>
       <c r="V34" s="1" t="s">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>30</v>
@@ -7830,48 +7830,34 @@
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>236</v>
-      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>237</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
       <c r="P37" s="1"/>
-      <c r="Q37" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q37" s="1"/>
       <c r="R37" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B38" s="1">
         <v>31124688</v>
@@ -7890,25 +7876,39 @@
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>238</v>
+      </c>
       <c r="M38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
+        <v>232</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
+      <c r="Q38" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R38" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>26</v>
@@ -8059,45 +8059,33 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>203</v>
-      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
       <c r="M41" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>261</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
       <c r="P41" s="1"/>
-      <c r="Q41" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q41" s="1"/>
       <c r="R41" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B42" s="1">
         <v>31294614</v>
@@ -8117,24 +8105,36 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
+      <c r="J42" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="M42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
+        <v>258</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
+      <c r="Q42" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R42" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
@@ -8166,48 +8166,42 @@
       <c r="H43" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1" t="s">
+      <c r="I43" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L43" s="1" t="s">
+      <c r="N43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="1" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B44" s="1">
         <v>31356652</v>
@@ -8228,14 +8222,18 @@
         <v>268</v>
       </c>
       <c r="H44" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
         <v>277</v>
       </c>
@@ -8243,22 +8241,24 @@
         <v>27</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="1" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U44" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V44" s="1" t="s">
         <v>278</v>
       </c>
@@ -8303,7 +8303,7 @@
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>30</v>
@@ -8584,9 +8584,15 @@
       <c r="F51" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="G51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -8630,15 +8636,9 @@
       <c r="F52" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -8677,55 +8677,41 @@
         <v>313</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="J53" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="P53" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
       <c r="R53" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B54" s="1">
         <v>31445216</v>
@@ -8737,32 +8723,46 @@
         <v>313</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="M54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
+        <v>313</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="R54" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -8897,7 +8897,7 @@
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
-        <v>29</v>
+        <v>333</v>
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
@@ -8914,12 +8914,12 @@
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B58" s="1">
         <v>31457815</v>
@@ -8943,7 +8943,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>335</v>
+        <v>29</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -9028,38 +9028,50 @@
         <v>30</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
+      <c r="J60" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="M60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
+        <v>339</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
+      <c r="Q60" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R60" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="1:22">
       <c r="A61" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B61" s="1">
         <v>31475270</v>
@@ -9074,41 +9086,29 @@
         <v>30</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-      <c r="J61" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>348</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
       <c r="P61" s="1"/>
-      <c r="Q61" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q61" s="1"/>
       <c r="R61" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
@@ -9155,7 +9155,7 @@
         <v>354</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R62" s="1" t="s">
         <v>30</v>
@@ -9261,7 +9261,7 @@
         <v>366</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R64" s="1" t="s">
         <v>30</v>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>30</v>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="P73" s="1"/>
       <c r="Q73" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R73" s="1" t="s">
         <v>30</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P76" s="1"/>
       <c r="Q76" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R76" s="1" t="s">
         <v>26</v>
@@ -9901,7 +9901,7 @@
         <v>27</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -9960,7 +9960,7 @@
         <v>430</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>425</v>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="P81" s="1"/>
       <c r="Q81" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R81" s="1" t="s">
         <v>30</v>
@@ -10298,7 +10298,7 @@
         <v>59</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M84" s="1" t="s">
         <v>468</v>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="P85" s="1"/>
       <c r="Q85" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R85" s="1" t="s">
         <v>26</v>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="P88" s="1"/>
       <c r="Q88" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R88" s="1" t="s">
         <v>30</v>
@@ -10657,7 +10657,7 @@
       </c>
       <c r="P90" s="1"/>
       <c r="Q90" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R90" s="1" t="s">
         <v>30</v>
@@ -10742,7 +10742,7 @@
         <v>417</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M92" s="1" t="s">
         <v>513</v>
@@ -10802,7 +10802,7 @@
         <v>245</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M93" s="1" t="s">
         <v>520</v>
@@ -10849,13 +10849,13 @@
         <v>27</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>527</v>
@@ -10920,7 +10920,7 @@
         <v>535</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M95" s="1" t="s">
         <v>533</v>
@@ -10962,7 +10962,7 @@
         <v>30</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>28</v>
@@ -10986,14 +10986,14 @@
         <v>542</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O96" s="1" t="s">
         <v>543</v>
       </c>
       <c r="P96" s="1"/>
       <c r="Q96" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R96" s="1" t="s">
         <v>30</v>
@@ -11106,7 +11106,7 @@
         <v>245</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M98" s="1" t="s">
         <v>555</v>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="P98" s="1"/>
       <c r="Q98" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R98" s="1" t="s">
         <v>30</v>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="P99" s="1"/>
       <c r="Q99" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R99" s="1" t="s">
         <v>30</v>
@@ -11603,10 +11603,10 @@
         <v>609</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M107" s="1" t="s">
         <v>608</v>
@@ -11619,7 +11619,7 @@
       </c>
       <c r="P107" s="1"/>
       <c r="Q107" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R107" s="1" t="s">
         <v>30</v>
@@ -11852,7 +11852,7 @@
         <v>30</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G112" s="1"/>
       <c r="H112" s="1"/>
@@ -11864,11 +11864,11 @@
         <v>59</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M112" s="1"/>
       <c r="N112" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O112" s="1" t="s">
         <v>637</v>
@@ -11909,7 +11909,7 @@
         <v>27</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>641</v>
@@ -11937,7 +11937,7 @@
       </c>
       <c r="P113" s="1"/>
       <c r="Q113" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R113" s="1" t="s">
         <v>30</v>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="P115" s="1"/>
       <c r="Q115" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R115" s="1" t="s">
         <v>30</v>
@@ -12333,7 +12333,7 @@
       </c>
       <c r="P120" s="1"/>
       <c r="Q120" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R120" s="1" t="s">
         <v>30</v>
@@ -12429,13 +12429,13 @@
         <v>27</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>696</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J122" s="1"/>
       <c r="K122" s="1"/>
@@ -12686,7 +12686,7 @@
         <v>30</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
@@ -12698,18 +12698,18 @@
         <v>564</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M127" s="1"/>
       <c r="N127" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O127" s="1" t="s">
         <v>720</v>
       </c>
       <c r="P127" s="1"/>
       <c r="Q127" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R127" s="1" t="s">
         <v>30</v>
@@ -12771,7 +12771,7 @@
       </c>
       <c r="P128" s="1"/>
       <c r="Q128" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R128" s="1" t="s">
         <v>30</v>
@@ -12816,7 +12816,7 @@
         <v>59</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M129" s="1" t="s">
         <v>735</v>
@@ -12829,7 +12829,7 @@
       </c>
       <c r="P129" s="1"/>
       <c r="Q129" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R129" s="1" t="s">
         <v>30</v>
@@ -12887,7 +12887,7 @@
       </c>
       <c r="P130" s="1"/>
       <c r="Q130" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R130" s="1" t="s">
         <v>30</v>
@@ -12932,7 +12932,7 @@
         <v>749</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M131" s="1"/>
       <c r="N131" s="1" t="s">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="P132" s="1"/>
       <c r="Q132" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R132" s="1" t="s">
         <v>30</v>
@@ -13170,7 +13170,7 @@
         <v>779</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M135" s="1" t="s">
         <v>780</v>
@@ -13214,7 +13214,7 @@
         <v>30</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G136" s="1" t="s">
         <v>784</v>
@@ -13287,7 +13287,7 @@
       </c>
       <c r="P137" s="1"/>
       <c r="Q137" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R137" s="1" t="s">
         <v>30</v>
@@ -13341,7 +13341,7 @@
       </c>
       <c r="P138" s="1"/>
       <c r="Q138" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R138" s="1" t="s">
         <v>30</v>
@@ -13564,7 +13564,7 @@
         <v>30</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
@@ -13582,14 +13582,14 @@
         <v>824</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O143" s="1" t="s">
         <v>825</v>
       </c>
       <c r="P143" s="1"/>
       <c r="Q143" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R143" s="1" t="s">
         <v>30</v>
@@ -13620,7 +13620,7 @@
         <v>30</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>28</v>
@@ -13644,7 +13644,7 @@
         <v>828</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O144" s="1" t="s">
         <v>832</v>
@@ -13692,7 +13692,7 @@
         <v>293</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M145" s="1" t="s">
         <v>836</v>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="P147" s="1"/>
       <c r="Q147" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R147" s="1" t="s">
         <v>30</v>
@@ -13863,7 +13863,7 @@
         <v>855</v>
       </c>
       <c r="K148" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L148" s="1" t="s">
         <v>856</v>
@@ -14010,7 +14010,7 @@
         <v>30</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
@@ -14064,7 +14064,7 @@
         <v>873</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M152" s="1"/>
       <c r="N152" s="1" t="s">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="P154" s="1"/>
       <c r="Q154" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R154" s="1" t="s">
         <v>30</v>
@@ -14233,7 +14233,7 @@
       </c>
       <c r="P155" s="1"/>
       <c r="Q155" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R155" s="1" t="s">
         <v>30</v>
@@ -14314,7 +14314,7 @@
         <v>30</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
@@ -14354,7 +14354,7 @@
         <v>30</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>28</v>
@@ -14577,7 +14577,7 @@
       </c>
       <c r="P162" s="1"/>
       <c r="Q162" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R162" s="1" t="s">
         <v>30</v>
@@ -14694,7 +14694,7 @@
         <v>30</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G165" s="1"/>
       <c r="H165" s="1"/>
@@ -14712,14 +14712,14 @@
         <v>932</v>
       </c>
       <c r="N165" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O165" s="1" t="s">
         <v>933</v>
       </c>
       <c r="P165" s="1"/>
       <c r="Q165" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R165" s="1" t="s">
         <v>30</v>
@@ -14808,7 +14808,7 @@
         <v>30</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G167" s="1"/>
       <c r="H167" s="1"/>
@@ -14817,21 +14817,21 @@
         <v>941</v>
       </c>
       <c r="K167" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L167" s="1" t="s">
         <v>942</v>
       </c>
       <c r="M167" s="1"/>
       <c r="N167" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O167" s="1" t="s">
         <v>943</v>
       </c>
       <c r="P167" s="1"/>
       <c r="Q167" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R167" s="1" t="s">
         <v>30</v>
@@ -14993,7 +14993,7 @@
       </c>
       <c r="P170" s="1"/>
       <c r="Q170" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R170" s="1" t="s">
         <v>30</v>
@@ -15053,7 +15053,7 @@
       </c>
       <c r="P171" s="1"/>
       <c r="Q171" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R171" s="1" t="s">
         <v>30</v>
@@ -15100,7 +15100,7 @@
         <v>967</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M172" s="1" t="s">
         <v>964</v>
@@ -15325,13 +15325,13 @@
         <v>27</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H176" s="1" t="s">
         <v>990</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J176" s="1" t="s">
         <v>991</v>
@@ -15340,7 +15340,7 @@
         <v>992</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M176" s="1" t="s">
         <v>989</v>
@@ -15398,7 +15398,7 @@
         <v>59</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M177" s="1"/>
       <c r="N177" s="1" t="s">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="P177" s="1"/>
       <c r="Q177" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R177" s="1" t="s">
         <v>30</v>
@@ -15471,7 +15471,7 @@
       </c>
       <c r="P178" s="1"/>
       <c r="Q178" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R178" s="1" t="s">
         <v>30</v>
@@ -15523,7 +15523,7 @@
       </c>
       <c r="P179" s="1"/>
       <c r="Q179" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R179" s="1" t="s">
         <v>26</v>
@@ -15694,7 +15694,7 @@
         <v>165</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M182" s="1" t="s">
         <v>1032</v>
@@ -15707,7 +15707,7 @@
       </c>
       <c r="P182" s="1"/>
       <c r="Q182" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R182" s="1" t="s">
         <v>30</v>
@@ -15785,13 +15785,13 @@
         <v>27</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H184" s="1" t="s">
         <v>1040</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J184" s="1"/>
       <c r="K184" s="1"/>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="P185" s="1"/>
       <c r="Q185" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R185" s="1" t="s">
         <v>26</v>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="P187" s="1"/>
       <c r="Q187" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R187" s="1" t="s">
         <v>26</v>
@@ -16008,7 +16008,7 @@
         <v>30</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G188" s="1"/>
       <c r="H188" s="1"/>
@@ -16075,7 +16075,7 @@
       </c>
       <c r="P189" s="1"/>
       <c r="Q189" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R189" s="1" t="s">
         <v>30</v>
@@ -16182,7 +16182,7 @@
         <v>1085</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M191" s="1" t="s">
         <v>1086</v>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="P191" s="1"/>
       <c r="Q191" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R191" s="1" t="s">
         <v>30</v>
@@ -16301,7 +16301,7 @@
         <v>1100</v>
       </c>
       <c r="K193" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L193" s="1" t="s">
         <v>1101</v>
@@ -16373,7 +16373,7 @@
       </c>
       <c r="P194" s="1"/>
       <c r="Q194" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R194" s="1" t="s">
         <v>30</v>
@@ -16435,7 +16435,7 @@
         <v>1117</v>
       </c>
       <c r="Q195" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R195" s="1" t="s">
         <v>26</v>
@@ -16657,7 +16657,7 @@
       </c>
       <c r="P199" s="1"/>
       <c r="Q199" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R199" s="1" t="s">
         <v>30</v>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="P201" s="1"/>
       <c r="Q201" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R201" s="1" t="s">
         <v>30</v>
@@ -16804,7 +16804,7 @@
         <v>30</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G202" s="1"/>
       <c r="H202" s="1"/>
@@ -16813,21 +16813,21 @@
         <v>1157</v>
       </c>
       <c r="K202" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L202" s="1" t="s">
         <v>203</v>
       </c>
       <c r="M202" s="1"/>
       <c r="N202" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O202" s="1" t="s">
         <v>1158</v>
       </c>
       <c r="P202" s="1"/>
       <c r="Q202" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R202" s="1" t="s">
         <v>30</v>
@@ -16863,13 +16863,13 @@
         <v>27</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J203" s="1" t="s">
         <v>1163</v>
@@ -16878,7 +16878,7 @@
         <v>59</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M203" s="1" t="s">
         <v>1162</v>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="P203" s="1"/>
       <c r="Q203" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R203" s="1" t="s">
         <v>30</v>
@@ -16949,7 +16949,7 @@
         <v>1171</v>
       </c>
       <c r="Q204" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R204" s="1" t="s">
         <v>26</v>
@@ -17009,7 +17009,7 @@
         <v>1178</v>
       </c>
       <c r="Q205" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R205" s="1" t="s">
         <v>26</v>
@@ -17111,7 +17111,7 @@
         <v>1191</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J207" s="1" t="s">
         <v>1192</v>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="P207" s="1"/>
       <c r="Q207" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R207" s="1" t="s">
         <v>30</v>
@@ -17245,7 +17245,7 @@
       </c>
       <c r="P209" s="1"/>
       <c r="Q209" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R209" s="1" t="s">
         <v>26</v>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="P210" s="1"/>
       <c r="Q210" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R210" s="1" t="s">
         <v>30</v>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="P211" s="1"/>
       <c r="Q211" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R211" s="1" t="s">
         <v>30</v>
@@ -17427,7 +17427,7 @@
       </c>
       <c r="P212" s="1"/>
       <c r="Q212" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R212" s="1" t="s">
         <v>30</v>
@@ -17462,16 +17462,16 @@
         <v>30</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J213" s="1" t="s">
         <v>1237</v>
@@ -17486,7 +17486,7 @@
         <v>1236</v>
       </c>
       <c r="N213" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O213" s="1" t="s">
         <v>1239</v>
@@ -17528,7 +17528,7 @@
         <v>30</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G214" s="1" t="s">
         <v>1242</v>
@@ -17548,7 +17548,7 @@
         <v>1236</v>
       </c>
       <c r="N214" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O214" s="1" t="s">
         <v>1239</v>
@@ -17663,10 +17663,10 @@
         <v>1256</v>
       </c>
       <c r="K216" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L216" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M216" s="1" t="s">
         <v>1257</v>
@@ -17737,7 +17737,7 @@
       </c>
       <c r="P217" s="1"/>
       <c r="Q217" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R217" s="1" t="s">
         <v>30</v>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="P218" s="1"/>
       <c r="Q218" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R218" s="1" t="s">
         <v>30</v>
@@ -17885,7 +17885,7 @@
         <v>1098</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H220" s="1"/>
       <c r="I220" s="1"/>
@@ -17909,7 +17909,7 @@
       </c>
       <c r="P220" s="1"/>
       <c r="Q220" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R220" s="1" t="s">
         <v>30</v>
@@ -17954,7 +17954,7 @@
         <v>1282</v>
       </c>
       <c r="L221" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M221" s="1" t="s">
         <v>1283</v>
@@ -17967,7 +17967,7 @@
       </c>
       <c r="P221" s="1"/>
       <c r="Q221" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R221" s="1" t="s">
         <v>30</v>
@@ -18018,7 +18018,7 @@
         <v>1289</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M222" s="1" t="s">
         <v>1290</v>
@@ -18095,7 +18095,7 @@
       </c>
       <c r="P223" s="1"/>
       <c r="Q223" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R223" s="1" t="s">
         <v>30</v>
@@ -18159,7 +18159,7 @@
       </c>
       <c r="P224" s="1"/>
       <c r="Q224" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R224" s="1" t="s">
         <v>30</v>
@@ -18219,7 +18219,7 @@
       </c>
       <c r="P225" s="1"/>
       <c r="Q225" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R225" s="1" t="s">
         <v>30</v>
@@ -18279,7 +18279,7 @@
       </c>
       <c r="P226" s="1"/>
       <c r="Q226" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R226" s="1" t="s">
         <v>30</v>
@@ -18399,7 +18399,7 @@
       </c>
       <c r="P228" s="1"/>
       <c r="Q228" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R228" s="1" t="s">
         <v>30</v>
@@ -18437,13 +18437,13 @@
         <v>27</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H229" s="1" t="s">
         <v>1338</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J229" s="1" t="s">
         <v>1339</v>
@@ -18465,7 +18465,7 @@
       </c>
       <c r="P229" s="1"/>
       <c r="Q229" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R229" s="1" t="s">
         <v>30</v>
@@ -18516,7 +18516,7 @@
         <v>165</v>
       </c>
       <c r="L230" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M230" s="1" t="s">
         <v>1349</v>
@@ -18529,7 +18529,7 @@
       </c>
       <c r="P230" s="1"/>
       <c r="Q230" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R230" s="1" t="s">
         <v>30</v>
@@ -18648,7 +18648,7 @@
         <v>417</v>
       </c>
       <c r="L232" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M232" s="1" t="s">
         <v>1365</v>
@@ -18661,7 +18661,7 @@
       </c>
       <c r="P232" s="1"/>
       <c r="Q232" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R232" s="1" t="s">
         <v>30</v>
@@ -18709,7 +18709,7 @@
         <v>1374</v>
       </c>
       <c r="K233" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L233" s="1" t="s">
         <v>1375</v>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="P233" s="1"/>
       <c r="Q233" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R233" s="1" t="s">
         <v>30</v>
@@ -18791,7 +18791,7 @@
       </c>
       <c r="P234" s="1"/>
       <c r="Q234" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R234" s="1" t="s">
         <v>30</v>
@@ -18855,7 +18855,7 @@
       </c>
       <c r="P235" s="1"/>
       <c r="Q235" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R235" s="1" t="s">
         <v>30</v>
@@ -18913,7 +18913,7 @@
       </c>
       <c r="P236" s="1"/>
       <c r="Q236" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R236" s="1" t="s">
         <v>30</v>
@@ -19035,7 +19035,7 @@
       </c>
       <c r="P238" s="1"/>
       <c r="Q238" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R238" s="1" t="s">
         <v>30</v>
@@ -19150,7 +19150,7 @@
         <v>1418</v>
       </c>
       <c r="L240" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M240" s="1" t="s">
         <v>1423</v>
@@ -19207,10 +19207,10 @@
         <v>1429</v>
       </c>
       <c r="K241" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M241" s="1" t="s">
         <v>1428</v>
@@ -19223,7 +19223,7 @@
       </c>
       <c r="P241" s="1"/>
       <c r="Q241" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R241" s="1" t="s">
         <v>30</v>
@@ -19283,7 +19283,7 @@
       </c>
       <c r="P242" s="1"/>
       <c r="Q242" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R242" s="1" t="s">
         <v>26</v>
@@ -19379,13 +19379,13 @@
         <v>27</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J244" s="1" t="s">
         <v>1440</v>
@@ -19469,7 +19469,7 @@
         <v>1454</v>
       </c>
       <c r="Q245" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R245" s="1" t="s">
         <v>30</v>
@@ -19582,7 +19582,7 @@
         <v>293</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M247" s="1" t="s">
         <v>1467</v>
@@ -19595,7 +19595,7 @@
       </c>
       <c r="P247" s="1"/>
       <c r="Q247" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R247" s="1" t="s">
         <v>30</v>
@@ -19644,7 +19644,7 @@
         <v>293</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M248" s="1" t="s">
         <v>1467</v>
@@ -19657,7 +19657,7 @@
       </c>
       <c r="P248" s="1"/>
       <c r="Q248" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R248" s="1" t="s">
         <v>30</v>
@@ -19777,7 +19777,7 @@
       </c>
       <c r="P250" s="1"/>
       <c r="Q250" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R250" s="1" t="s">
         <v>30</v>
@@ -20188,7 +20188,7 @@
         <v>1534</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M257" s="1" t="s">
         <v>1530</v>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="P257" s="1"/>
       <c r="Q257" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R257" s="1" t="s">
         <v>30</v>
@@ -20250,7 +20250,7 @@
         <v>1534</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M258" s="1" t="s">
         <v>1540</v>
@@ -20263,7 +20263,7 @@
       </c>
       <c r="P258" s="1"/>
       <c r="Q258" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R258" s="1" t="s">
         <v>30</v>
@@ -20374,7 +20374,7 @@
         <v>443</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M260" s="1" t="s">
         <v>1555</v>
@@ -20387,7 +20387,7 @@
       </c>
       <c r="P260" s="1"/>
       <c r="Q260" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R260" s="1" t="s">
         <v>30</v>
@@ -20432,7 +20432,7 @@
         <v>293</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M261" s="1" t="s">
         <v>1562</v>
@@ -20483,13 +20483,13 @@
         <v>27</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J262" s="1" t="s">
         <v>1567</v>
@@ -20511,7 +20511,7 @@
       </c>
       <c r="P262" s="1"/>
       <c r="Q262" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R262" s="1" t="s">
         <v>30</v>
@@ -20571,7 +20571,7 @@
       </c>
       <c r="P263" s="1"/>
       <c r="Q263" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R263" s="1" t="s">
         <v>30</v>
@@ -20622,7 +20622,7 @@
         <v>1585</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="M264" s="1" t="s">
         <v>1586</v>
@@ -20635,7 +20635,7 @@
       </c>
       <c r="P264" s="1"/>
       <c r="Q264" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R264" s="1" t="s">
         <v>30</v>
@@ -20686,7 +20686,7 @@
         <v>417</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M265" s="1" t="s">
         <v>1591</v>
@@ -20748,7 +20748,7 @@
         <v>417</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M266" s="1" t="s">
         <v>1591</v>
@@ -20812,7 +20812,7 @@
         <v>59</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M267" s="1" t="s">
         <v>1603</v>
@@ -20876,7 +20876,7 @@
         <v>59</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M268" s="1" t="s">
         <v>1612</v>
@@ -20925,13 +20925,13 @@
         <v>209</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H269" s="1" t="s">
         <v>1619</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J269" s="1" t="s">
         <v>1620</v>
@@ -20955,7 +20955,7 @@
         <v>1623</v>
       </c>
       <c r="Q269" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R269" s="1" t="s">
         <v>30</v>
@@ -20991,13 +20991,13 @@
         <v>209</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H270" s="1" t="s">
         <v>1619</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J270" s="1" t="s">
         <v>1620</v>
@@ -21021,7 +21021,7 @@
         <v>1623</v>
       </c>
       <c r="Q270" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R270" s="1" t="s">
         <v>30</v>
@@ -21083,7 +21083,7 @@
       </c>
       <c r="P271" s="1"/>
       <c r="Q271" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R271" s="1" t="s">
         <v>30</v>
@@ -21147,7 +21147,7 @@
       </c>
       <c r="P272" s="1"/>
       <c r="Q272" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R272" s="1" t="s">
         <v>30</v>
@@ -21211,7 +21211,7 @@
       </c>
       <c r="P273" s="1"/>
       <c r="Q273" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R273" s="1" t="s">
         <v>30</v>
@@ -21271,7 +21271,7 @@
       </c>
       <c r="P274" s="1"/>
       <c r="Q274" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R274" s="1" t="s">
         <v>30</v>
@@ -21391,7 +21391,7 @@
       </c>
       <c r="P276" s="1"/>
       <c r="Q276" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R276" s="1" t="s">
         <v>30</v>
@@ -21517,7 +21517,7 @@
       </c>
       <c r="P278" s="1"/>
       <c r="Q278" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R278" s="1" t="s">
         <v>30</v>
@@ -21687,7 +21687,7 @@
       </c>
       <c r="P281" s="1"/>
       <c r="Q281" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R281" s="1" t="s">
         <v>30</v>
@@ -21755,7 +21755,7 @@
         <v>1714</v>
       </c>
       <c r="Q282" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R282" s="1" t="s">
         <v>30</v>
